--- a/services_forms/009_it_request_form--services_forms.xlsx
+++ b/services_forms/009_it_request_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>urgency_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>Urgency 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>priority_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>Priority 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>submit_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>submit_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>urgency_choices</t>
+          <t>urgency_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>urgency_choices</t>
+          <t>urgency_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>priority_choices</t>
+          <t>priority_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>priority_choices</t>
+          <t>priority_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
